--- a/RESULTS/result_370FL_15A_with_prep.xlsx
+++ b/RESULTS/result_370FL_15A_with_prep.xlsx
@@ -60,7 +60,7 @@
     <t>Nbr_sts_used</t>
   </si>
   <si>
-    <t>370FL_15A_2</t>
+    <t>370FL_15A_1</t>
   </si>
 </sst>
 </file>
@@ -470,19 +470,19 @@
         <v>0.0</v>
       </c>
       <c r="G2">
-        <v>18158</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>47.1398</v>
+        <v>0.0537</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>1.0</v>
+        <v>-0.0</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -490,34 +490,34 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="C3">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D3">
-        <v>39.99999800353961</v>
+        <v>0.0</v>
       </c>
       <c r="E3">
         <v>0.0</v>
       </c>
       <c r="F3">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
       <c r="G3">
-        <v>99935</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>180.0131</v>
+        <v>0.0905</v>
       </c>
       <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>-0.0</v>
+      </c>
+      <c r="K3">
         <v>0</v>
-      </c>
-      <c r="J3">
-        <v>1.0</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
